--- a/ЛР2-3_Объем_рынка/Excel/ПЛ_платежеспособность_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ПЛ_платежеспособность_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772AFA08-36E2-4AF0-918A-FD18FF61C6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D0B219-C388-4EE1-B389-8B276E934185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,20 @@
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -724,9 +738,6 @@
     <t>Денежного эффекта у студента нет (продукт Free); показано для случая покупки Pro</t>
   </si>
   <si>
-    <t>стипендия БГУИР (ИТ), середина диапазона 224,66–342,34 BYN (вторичный источник)</t>
-  </si>
-  <si>
     <t>Эффект = доход × доля сэкономленного времени (3 ч из 168 ч в месяц; допущение Д-07, 🔲 опрос)</t>
   </si>
   <si>
@@ -803,6 +814,9 @@
   </si>
   <si>
     <t>отчёт ЛР1, без скриншота; 30.09.2026. Доля РБ — допущение Д-01. H = CR1 × CR2 (в шаблоне отдельной конверсии в оплату нет)</t>
+  </si>
+  <si>
+    <t>стипендия БГУИР (ИКТ), середина диапазона 229,75–367,60 BYN (таблица БГУИР с 01.08.2026)</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1670,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -1788,7 +1802,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="42.75">
+    <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1824,7 +1838,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -1860,7 +1874,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="42.75">
+    <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -1896,7 +1910,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1932,7 +1946,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="42.75">
+    <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
@@ -1968,7 +1982,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="42.75">
+    <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -7336,7 +7350,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -7474,7 +7488,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="3" t="s">
         <v>163</v>
       </c>
@@ -7488,7 +7502,7 @@
         <v>166</v>
       </c>
       <c r="E5" s="15">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>167</v>
@@ -7514,7 +7528,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="3" t="s">
         <v>168</v>
       </c>
@@ -7528,7 +7542,7 @@
         <v>171</v>
       </c>
       <c r="E6" s="15">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>172</v>
@@ -7554,7 +7568,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="3" t="s">
         <v>173</v>
       </c>
@@ -7568,7 +7582,7 @@
         <v>176</v>
       </c>
       <c r="E7" s="15">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>177</v>
@@ -7594,7 +7608,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
         <v>178</v>
       </c>
@@ -7608,7 +7622,7 @@
         <v>181</v>
       </c>
       <c r="E8" s="15">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>182</v>
@@ -7634,7 +7648,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="57">
+    <row r="9" spans="1:26" ht="54">
       <c r="A9" s="3" t="s">
         <v>75</v>
       </c>
@@ -7645,10 +7659,10 @@
         <v>184</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E9" s="15">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>185</v>
@@ -7674,7 +7688,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="42.75">
+    <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -7685,7 +7699,7 @@
         <v>188</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
@@ -7740,21 +7754,21 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="85.5">
+    <row r="12" spans="1:26" ht="81">
       <c r="A12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E12" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -7780,19 +7794,19 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="E13" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -13064,7 +13078,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -13193,7 +13207,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="71.25">
+    <row r="5" spans="1:26" ht="67.5">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -13329,7 +13343,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="42.75">
+    <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -13363,7 +13377,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="28.5">
+    <row r="10" spans="1:26" ht="27">
       <c r="A10" s="3" t="s">
         <v>47</v>
       </c>
@@ -13397,7 +13411,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="42.75">
+    <row r="11" spans="1:26" ht="27">
       <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
@@ -13436,7 +13450,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="5">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>50</v>
@@ -18741,7 +18755,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -18895,7 +18909,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="42.75">
+    <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="3" t="s">
         <v>195</v>
       </c>
@@ -18950,7 +18964,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
         <v>198</v>
       </c>
@@ -19005,7 +19019,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="57">
+    <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
         <v>201</v>
       </c>
@@ -19347,7 +19361,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="15">
+    <row r="16" spans="1:26" ht="13.9">
       <c r="A16" s="6" t="s">
         <v>64</v>
       </c>
@@ -19414,12 +19428,12 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="285">
+    <row r="18" spans="1:26" ht="256.5">
       <c r="A18" s="2" t="s">
         <v>204</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -24557,7 +24571,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="5" width="16" customWidth="1"/>
@@ -24704,7 +24718,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="42.75">
+    <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="3" t="s">
         <v>205</v>
       </c>
@@ -24753,7 +24767,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
         <v>208</v>
       </c>
@@ -24802,7 +24816,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="42.75">
+    <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
         <v>210</v>
       </c>
@@ -24851,7 +24865,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
         <v>212</v>
       </c>
@@ -24900,7 +24914,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="28.5">
+    <row r="9" spans="1:26" ht="27">
       <c r="A9" s="3" t="s">
         <v>214</v>
       </c>
@@ -24949,7 +24963,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="28.5">
+    <row r="10" spans="1:26" ht="27">
       <c r="A10" s="3" t="s">
         <v>216</v>
       </c>
@@ -24998,7 +25012,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="28.5">
+    <row r="11" spans="1:26" ht="27">
       <c r="A11" s="3" t="s">
         <v>218</v>
       </c>
@@ -25047,7 +25061,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="28.5">
+    <row r="12" spans="1:26" ht="27">
       <c r="A12" s="3" t="s">
         <v>220</v>
       </c>
@@ -25124,7 +25138,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="15">
+    <row r="14" spans="1:26" ht="13.9">
       <c r="A14" s="6" t="s">
         <v>76</v>
       </c>
@@ -25203,7 +25217,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="28.5">
+    <row r="16" spans="1:26" ht="27">
       <c r="A16" s="2" t="s">
         <v>222</v>
       </c>
@@ -25233,7 +25247,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="42.75">
+    <row r="17" spans="1:26" ht="27">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -25247,7 +25261,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -25301,7 +25315,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="28.5">
+    <row r="19" spans="1:26" ht="27">
       <c r="A19" s="2" t="s">
         <v>227</v>
       </c>
@@ -25363,7 +25377,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="171">
+    <row r="21" spans="1:26" ht="148.5">
       <c r="A21" s="2" t="s">
         <v>229</v>
       </c>
@@ -30420,7 +30434,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -30572,12 +30586,12 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="57">
+    <row r="5" spans="1:26" ht="67.5">
       <c r="A5" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B5" s="7">
-        <v>283.5</v>
+        <v>298.68</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
@@ -30608,7 +30622,7 @@
         <v>230</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -30626,7 +30640,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="57">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
         <v>198</v>
       </c>
@@ -30659,10 +30673,10 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -30680,7 +30694,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="57">
+    <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
         <v>201</v>
       </c>
@@ -30713,10 +30727,10 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -30962,13 +30976,13 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="30">
+    <row r="14" spans="1:26" ht="27.75">
       <c r="A14" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B14" s="9">
         <f t="shared" ref="B14:H14" si="4">AVERAGE(B5:B12)</f>
-        <v>3289.5</v>
+        <v>3294.56</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="4"/>
@@ -31041,9 +31055,9 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="85.5">
+    <row r="16" spans="1:26" ht="81">
       <c r="A16" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -36238,7 +36252,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -36385,19 +36399,19 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="57">
+    <row r="5" spans="1:26" ht="54">
       <c r="A5" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B5" s="7">
-        <v>14.18</v>
+        <v>14.93</v>
       </c>
       <c r="C5" s="7">
         <v>10.095000000000001</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" ref="D5:D12" si="0">IF(A5="","",B5/C5)</f>
-        <v>1.4046557701832589</v>
+        <v>1.4789499752352648</v>
       </c>
       <c r="E5" s="3" t="str">
         <f t="shared" ref="E5:E12" si="1">IF(A5="","",IF(D5&gt;=1.5,"высокая",IF(D5&gt;=1,"достаточная",IF(D5&gt;=0.7,"пограничная","низкая"))))</f>
@@ -36418,7 +36432,7 @@
         <v>728202.82499999995</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -36437,7 +36451,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
         <v>198</v>
       </c>
@@ -36470,7 +36484,7 @@
         <v>830278.41749999998</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -36489,7 +36503,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="42.75">
+    <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
         <v>201</v>
       </c>
@@ -36522,7 +36536,7 @@
         <v>41429.879999999997</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -36769,13 +36783,13 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="15">
+    <row r="14" spans="1:26" ht="13.9">
       <c r="A14" s="6" t="s">
         <v>97</v>
       </c>
       <c r="B14" s="9">
         <f>AVERAGE(B5:B12)</f>
-        <v>164.47666666666666</v>
+        <v>164.72666666666666</v>
       </c>
       <c r="C14" s="9">
         <f>AVERAGE(C5:C12)</f>
@@ -36783,7 +36797,7 @@
       </c>
       <c r="D14" s="12">
         <f>AVERAGE(D5:D12)</f>
-        <v>16.292884266138351</v>
+        <v>16.317649001155687</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="10">
@@ -42055,7 +42069,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -42192,7 +42206,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="42.75">
+    <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="3" t="s">
         <v>103</v>
       </c>
@@ -42230,7 +42244,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -42268,7 +42282,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="3" t="s">
         <v>107</v>
       </c>
@@ -42306,7 +42320,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
         <v>109</v>
       </c>
@@ -42344,7 +42358,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="42.75">
+    <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="3" t="s">
         <v>111</v>
       </c>
@@ -42482,7 +42496,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="57">
+    <row r="13" spans="1:26" ht="54">
       <c r="A13" s="3" t="str">
         <f>IF('02_Сегменты'!A5="","",'02_Сегменты'!A5)</f>
         <v>S-01 Студенты технических и экономических специальностей</v>
@@ -42534,7 +42548,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="42.75">
+    <row r="14" spans="1:26" ht="40.5">
       <c r="A14" s="3" t="str">
         <f>IF('02_Сегменты'!A6="","",'02_Сегменты'!A6)</f>
         <v>S-02/S-03 Аналитики, архитекторы ПО и разработчики</v>
@@ -42586,7 +42600,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="28.5">
+    <row r="15" spans="1:26" ht="27">
       <c r="A15" s="3" t="str">
         <f>IF('02_Сегменты'!A7="","",'02_Сегменты'!A7)</f>
         <v>S-04 Преподаватели технических дисциплин</v>
@@ -42926,7 +42940,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="15">
+    <row r="22" spans="1:26" ht="13.9">
       <c r="A22" s="6" t="s">
         <v>64</v>
       </c>
@@ -47973,7 +47987,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="6" width="18" customWidth="1"/>
@@ -48124,9 +48138,9 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="85.5">
+    <row r="5" spans="1:26" ht="81">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B5" s="7">
         <v>507000</v>
@@ -48162,7 +48176,7 @@
         <v>120.25640484000002</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -48179,9 +48193,9 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="71.25">
+    <row r="6" spans="1:26" ht="67.5">
       <c r="A6" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B6" s="7">
         <v>7800000</v>
@@ -48217,7 +48231,7 @@
         <v>1850.0985360000002</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -48234,9 +48248,9 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="99.75">
+    <row r="7" spans="1:26" ht="94.5">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B7" s="7">
         <v>678500</v>
@@ -48272,7 +48286,7 @@
         <v>160.93485342000002</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -48289,9 +48303,9 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="99.75">
+    <row r="8" spans="1:26" ht="94.5">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B8" s="7">
         <v>20000</v>
@@ -48321,7 +48335,7 @@
         <v>4.743842400000001</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -48514,7 +48528,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="15">
+    <row r="14" spans="1:26" ht="13.9">
       <c r="A14" s="6" t="s">
         <v>97</v>
       </c>
@@ -48602,9 +48616,9 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="114">
+    <row r="16" spans="1:26" ht="108">
       <c r="A16" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -53799,7 +53813,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -53937,7 +53951,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="3" t="s">
         <v>140</v>
       </c>
@@ -53982,7 +53996,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
@@ -54027,13 +54041,13 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B7" s="11">
         <f>'05_Платежеспособность'!D14</f>
-        <v>16.292884266138351</v>
+        <v>16.317649001155687</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>146</v>
@@ -54072,7 +54086,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
         <v>148</v>
       </c>
@@ -54177,7 +54191,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="28.5">
+    <row r="11" spans="1:26" ht="27">
       <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
@@ -54212,7 +54226,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="28.5">
+    <row r="12" spans="1:26" ht="27">
       <c r="A12" s="3" t="s">
         <v>153</v>
       </c>
@@ -54303,7 +54317,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="15">
+    <row r="15" spans="1:26" ht="13.9">
       <c r="A15" s="20" t="s">
         <v>155</v>
       </c>
